--- a/Foerderprogramme_EU_DE_2026.xlsx
+++ b/Foerderprogramme_EU_DE_2026.xlsx
@@ -16,9 +16,9 @@
     <sheet name="05_Quellen" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">01_EU_Programme!$A$2:$Q$23</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">02_DE_Programme!$A$2:$Q$11</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">03_Deadlines!$A$5:$G$25</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">01_EU_Programme!$A$2:$Q$26</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">02_DE_Programme!$A$2:$Q$13</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">03_Deadlines!$A$5:$G$29</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="718">
   <si>
     <t xml:space="preserve">Foerderprogramme EU &amp; Deutschland fuer Deep-Tech / AI-Startups und Mittelstand</t>
   </si>
@@ -134,7 +134,70 @@
     <t xml:space="preserve">In der Anfrage wurde ein Screenshot zur 'USA-Foerderung rechter Projekte' erwaehnt. Dieser Anfrage lag KEIN Bild bei und im Repository liegt keine Bilddatei. Es wurde daher nichts dazu geprueft und bewusst auch nichts dazu vermutet oder rekonstruiert. Bitte den Screenshot nachreichen - dann wird er separat ausgewertet.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Methodik und Grenzen</t>
+    <t xml:space="preserve">5. Korrekturen nach unabhaengiger Faktenpruefung (11.08.2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warum das hier steht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Datei wurde nach der Ersterstellung von einem zweiten, unabhaengigen Pruefdurchlauf gegen die Primaerquellen kontrolliert. Dabei sind acht Sachfehler gefunden und korrigiert worden. Sie stehen hier, damit nachvollziehbar bleibt, was sich geaendert hat - und damit niemand mit einer aelteren Fassung weiterarbeitet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZIM-Foerderhoehe war falsch: 690.000 / 560.000 / 280.000 EUR sind ZUWENDUNGSFAEHIGE KOSTEN, nicht Foerderbetraege. Der Zuschuss ergibt sich erst aus Kosten x Foerdersatz. Ein kleines Unternehmen im Kooperationsprojekt bekommt also rund 252.000 EUR, nicht 560.000 EUR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZIM-Foerdersaetze waren falsch etikettiert: die genannten 55/50/45/40/30 % gelten fuer KOOPERATIONSPROJEKTE, nicht fuer nationale Projekte allgemein. Fuer Einzelprojekte gelten 45/45/40/35/25 % - Abweichung bis 10 Prozentpunkte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZIM-Zielgruppe war falsch eingeengt: kleine Unternehmen sind fuer Einzel- UND Kooperationsprojekte antragsberechtigt. Die Kooperationsauflage gilt nur fuer Unternehmen bis 999 Beschaeftigte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIC Transition: die 18-Monats-Regel fuer LAUFENDE Vorprojekte fehlte komplett. Der Grant-Start muss mehr als 18 Monate vor dem Cut-off liegen (Ausnahme ERC PoC: 6 Monate). Ein gerade gestartetes Vorprojekt qualifiziert nicht. Ausserdem war die Liste der foerderfaehigen Vorprojekte unvollstaendig.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forschungszulage: der Verweis lautet richtig Paragraf 7 Abs. 2 SATZ 1 FZulG. Wichtiger: nach Paragraf 3 Abs. 6 FZulG gilt die 12-Mio-Bemessungsgrundlage bei VERBUNDENEN UNTERNEHMEN nur einmal insgesamt - bei mehreren eigenen Firmen ist das der entscheidende Punkt und fehlte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXIST-Sachmittel waren vertauscht: 30.000 EUR gelten fuer TEAMS, bis 10.000 EUR fuer Einzelgruendungen - nicht umgekehrt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVEST laeuft zum 31.12.2026 aus. Das fehlte und ist ein K.-o.-Faktor fuer jede Angel-Runde, die spaeter geplant ist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xecs Call 6: Deutschland ist KEIN teilnehmendes Land - ein deutscher Partner kann dort nur selbstfinanziert mitmachen. Ausserdem: der Canada Call 7 listet nur Kanada, taugt also nicht als 'naechste Frist' fuer dieses Profil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neu aufgenommen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPRIND, KfW/ERP-Kredite, ERC Proof of Concept, MSCA und Eureka Innowwide waren in der ersten Fassung nicht enthalten und wurden ergaenzt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Methodik und Grenzen</t>
   </si>
   <si>
     <t xml:space="preserve">Primaerquellen</t>
@@ -317,7 +380,7 @@
     <t xml:space="preserve">Start bei niedrigem TRL, Ziel TRL 3-4</t>
   </si>
   <si>
-    <t xml:space="preserve">Kein starres Minimum - Einzelantragsteller ausdruecklich zugelassen. Empfohlen wird ein eigenes Arbeitspaket fuer Portfolio-Aktivitaeten mit mind. 10 Personenmonaten.</t>
+    <t xml:space="preserve">Kein starres Minimum - Einzelantragsteller ausdruecklich zugelassen, ABER: bei Einzelantraegen sind Mid-Caps und groessere Unternehmen NICHT zugelassen (nur KMU, Start-ups, Forschungseinrichtungen, natuerliche Personen). Empfohlen wird ein eigenes Arbeitspaket fuer Portfolio-Aktivitaeten mit mind. 10 Personenmonaten.</t>
   </si>
   <si>
     <t xml:space="preserve">Bis 4 Mio EUR; hoehere Betraege moeglich, wenn begruendet. Call-Budget 96 Mio EUR, etwa gleich auf die 3 Challenges verteilt.</t>
@@ -359,7 +422,7 @@
     <t xml:space="preserve">Frist 16.09.2026, 17:00 Bruesseler Zeit.</t>
   </si>
   <si>
-    <t xml:space="preserve">Zwingend: die Ergebnisse muessen aus einem foerderfaehigen Vorprojekt stammen - EIC Pathfinder, ERC Proof of Concept, Horizon Europe Saeule 2, FET Innovation Launchpad oder (neu ab 2026) Horizon-Europe-/H2020-Forschungsinfrastrukturen. Zeitfenster: Vorprojekt laeuft noch oder Ende liegt weniger als 24 Monate vor dem Cut-off; bei ERC PoC muss der Start mehr als 6 Monate vor dem Cut-off liegen. Grantnummer und Akronym des Vorprojekts sind im Antrag anzugeben. Man muss NICHT selbst am Vorprojekt beteiligt gewesen sein - dann ist aber ein Commitment Letter des Rechteinhabers zu FRAND-Zugang beizulegen. Ausschliesslich zivile Anwendungen. Der Weg zum Markt ist im Antrag festzulegen (Eigenverwertung, Spin-off, Lizenzierung an Dritte oder anderer Weg).</t>
+    <t xml:space="preserve">Zwingend: die Ergebnisse muessen aus einem foerderfaehigen Vorprojekt stammen - EIC Pathfinder (inkl. H2020 FET-Open, FET-Proactive, FET Innovation Launchpad, FET Flagships), ERC Proof of Concept (H2020 oder Horizon Europe), RIAs aus H2020 Societal Challenges und Leadership in Industrial Technologies sowie Horizon Europe Saeule II, EDF- und PADR-Forschungsprojekte (nur bei ziviler Ausrichtung, Dual-use zulaessig) und (neu ab 2026) RIAs aus dem Bereich Forschungsinfrastrukturen in Horizon Europe/H2020. Ausserdem: das Ergebnis muss TRL 3 vollstaendig abgeschlossen haben und darf nicht ueber TRL 4 hinaus sein - andere TRL-Stufen sind nicht foerderfaehig. ZWEI Zeitfenster - beides harte Ausschlusskriterien: (a) LAUFENDES Vorprojekt - der Grant-Start muss mehr als 18 Monate vor dem Cut-off liegen; Ausnahme ERC Proof of Concept, dort genuegen mehr als 6 Monate. (b) ABGESCHLOSSENES Vorprojekt - das Ende darf weniger als 24 Monate vor dem Cut-off liegen. Ein gerade erst gestartetes Vorprojekt qualifiziert also NICHT. Grantnummer und Akronym des Vorprojekts sind im Antrag anzugeben. Man muss NICHT selbst am Vorprojekt beteiligt gewesen sein - dann ist aber ein Commitment Letter des Rechteinhabers zu FRAND-Zugang beizulegen. Ausschliesslich zivile Anwendungen. Der Weg zum Markt ist im Antrag festzulegen (Eigenverwertung, Spin-off, Lizenzierung an Dritte oder anderer Weg).</t>
   </si>
   <si>
     <t xml:space="preserve">Ohne foerderfaehiges Vorprojekt ist Transition schlicht nicht zugaenglich - das ist der zentrale Filter. Grants ueber Financial Support to Third Parties (z. B. ERA-NETs, EIT-KICs) zaehlen ausdruecklich NICHT als Vorprojekt. Pro foerderfaehigem ERC-PoC-/FET-Launchpad-Projekt ist nur ein Antrag moeglich. Coaching ist verpflichtend, sofern nicht gut begruendet abbedungen.</t>
@@ -482,7 +545,7 @@
     <t xml:space="preserve">Skalierungsphase</t>
   </si>
   <si>
-    <t xml:space="preserve">Bis 30 Mio EUR Direktbeteiligung. Call-Budget 100 Mio EUR.</t>
+    <t xml:space="preserve">10 bis 30 Mio EUR Direktbeteiligung (Untergrenze wie bei STEP Scale Up). Call-Budget 100 Mio EUR.</t>
   </si>
   <si>
     <t xml:space="preserve">Reine Beteiligung.</t>
@@ -551,7 +614,7 @@
     <t xml:space="preserve">Standard-Horizon-Regel: mind. 3 unabhaengige Rechtspersonen, davon mind. 1 in einem EU-Mitgliedstaat und 2 weitere in unterschiedlichen MS/assoziierten Laendern. Abweichungen je Topic moeglich.</t>
   </si>
   <si>
-    <t xml:space="preserve">Topic-abhaengig, typisch 2 bis 20 Mio EUR EU-Beitrag pro Projekt. Arbeitsprogramm 2026-2027 gesamt rund 1,5 Mrd EUR, davon rund 678 Mio EUR fuer digitale Destinationen und Topics.</t>
+    <t xml:space="preserve">Arbeitsprogramm 2026-2027 gesamt rund 1,5 Mrd EUR, davon rund 678,3 Mio EUR fuer digitale Destinationen und Topics. Der EU-Beitrag je Projekt steht ausschliesslich im jeweiligen Topic - eine programmweite Spanne laesst sich nicht serioes angeben.</t>
   </si>
   <si>
     <t xml:space="preserve">RIA 100 %; IA 70 % fuer gewinnorientierte Einrichtungen, 100 % fuer Non-Profit; CSA 100 %.</t>
@@ -587,7 +650,7 @@
     <t xml:space="preserve">Kein Forschungsprogramm - Fokus auf Kapazitaetsaufbau und breite Einfuehrung reifer Technologien (hoehere TRL).</t>
   </si>
   <si>
-    <t xml:space="preserve">Die meisten Topics 2026 verlangen 5 bis 7 Partner aus ebenso vielen Laendern (topic-abhaengig).</t>
+    <t xml:space="preserve">Topic-abhaengig. DIGITAL-Standard ist eine Mindestzahl von Antragstellern aus mehreren Laendern (haeufig 3 aus 3); einzelne Topics lassen Einzelantragsteller zu. Die konkrete Anforderung steht im jeweiligen Call-Fiche - eine pauschale Zahl gibt es nicht.</t>
   </si>
   <si>
     <t xml:space="preserve">Topic-abhaengig. Gesamtbudget 2021-2027 ueber 8,1 Mrd EUR. Beispiele 2026: 63,2 Mio EUR fuer KI-Innovation in Gesundheit und Online-Sicherheit; 204 Mio EUR fuer Digitalisierung von Unternehmen und digitale Kompetenzen.</t>
@@ -647,7 +710,7 @@
     <t xml:space="preserve">Kurzer Antrag mit Begruendung der Relevanz; Pruefung auf Foerderfaehigkeit und technische Machbarkeit. Antrag ueber access.eurohpc-ju.europa.eu. In der EU bestehen 19 AI Factories und 13 AI Factory Antennas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kein Cash-Zufluss - aber fuer ein AI-Startup oft der schnellste realisierbare Wert ueberhaupt: GPU-Kosten sind meist der groesste Posten, und hier faellt der Antragsaufwand auf Stunden statt Monate. Sollte in JEDEM Fall vor den grossen Zuschussantraegen gemacht werden. Achtung: der Playground-Zugang war zwischenzeitlich temporaer geschlossen - aktuellen Status vor dem Antrag pruefen.</t>
+    <t xml:space="preserve">Kein Cash-Zufluss - aber fuer ein AI-Startup oft der schnellste realisierbare Wert ueberhaupt: GPU-Kosten sind meist der groesste Posten, und hier faellt der Antragsaufwand auf Stunden statt Monate. Sollte in JEDEM Fall vor den grossen Zuschussantraegen gemacht werden. Achtung: sowohl Playground als auch Fast Lane waren zwischenzeitlich temporaer geschlossen - aktuellen Status je Zugangsmodus vor dem Antrag pruefen.</t>
   </si>
   <si>
     <t xml:space="preserve">B - Offizielle Website (EuroHPC JU)</t>
@@ -671,7 +734,7 @@
     <t xml:space="preserve">Internationales Konsortium; genaue Mindestanforderungen im jeweiligen Call-Dokument.</t>
   </si>
   <si>
-    <t xml:space="preserve">National geregelt; ITEA-Projekte sind typischerweise gross (mehrere Mio EUR Gesamtvolumen ueber alle Partner).</t>
+    <t xml:space="preserve">National geregelt. ITEA selbst veroeffentlicht keine Projektvolumina - Groessenordnung vorab mit dem nationalen Projekttraeger klaeren.</t>
   </si>
   <si>
     <t xml:space="preserve">National geregelt.</t>
@@ -707,90 +770,93 @@
     <t xml:space="preserve">Internationales Konsortium; Details im Call-Dokument.</t>
   </si>
   <si>
-    <t xml:space="preserve">Xecs Call 6 - 2026 laeuft. Matchmaking-Event 6./7. Oktober 2026 in Wien. Genaue Fristen ueber eurekanetwork.org bzw. xecs.eu pruefen.</t>
+    <t xml:space="preserve">Call geoeffnet 23.06.2026. Project Outline bis 21.01.2027. Matchmaking-Event 6./7. Oktober 2026 in Wien.</t>
   </si>
   <si>
     <t xml:space="preserve">Fokus auf elektronische Komponenten und Systeme (ECS). Antragsteller sollen die nationalen Foerderstellen vorab kontaktieren.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nur relevant bei Hardware-/Embedded-Bezug. Fuer reine Software-/AI-Vorhaben ist ITEA 4 der passendere Cluster. Fristen 2026 waren zum Recherchezeitpunkt nicht aus einer Primaerquelle bestaetigt - vor Planung verifizieren.</t>
+    <t xml:space="preserve">K.-o.-Kriterium fuer Sie: DEUTSCHLAND IST IN CALL 6 KEIN TEILNEHMENDES LAND. Auf der offiziellen Call-Seite ist keine deutsche Foerderstelle mit Foerdermodalitaeten gelistet - ein deutscher Partner kann also nur selbstfinanziert mitmachen. Ausserdem nur bei Hardware-/Embedded-Bezug relevant; fuer reine Software-/AI-Vorhaben ist ITEA 4 der passende Cluster.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B - Offizielle Call-Seite (Laenderliste und Fristen geprueft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eurekanetwork.org/programmes-and-calls/eureka-clusters/xecs-call-6-2026/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eureka Globalstars / Network Projects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eureka-Netzwerk; Foerderung national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMU, Grossunternehmen, Hochschulen, Forschungseinrichtungen, Non-Profits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottom-up, keine TRL-Vorgabe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mind. 2 voneinander unabhaengige Entitaeten; mind. 1 aus einem am Call teilnehmenden Eureka-Land und mind. 1 weitere unabhaengige aus dem jeweiligen Globalstars-Partnerland.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call-abhaengig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rollierende bilaterale Calls. ACHTUNG bei der Auswahl: der oft zuerst sichtbare Canada Call 7 (Frist 27.08.2026) laeuft unter Network Projects und listet als teilnehmendes Land nur Kanada - fuer deutsche Partner ohne eigene nationale Foerderung wertlos. Aktuelle Calls und teilnehmende Laender einzeln unter eurekanetwork.org pruefen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projekt muss auf Forschung/Entwicklung eines Produkts, Prozesses oder einer Dienstleistung gerichtet sein und ausschliesslich zivile, nicht-militaerische Anwendungen verfolgen. Kein einzelnes Unternehmen und kein einzelnes Land darf mehr als 70 % des Projektbudgets tragen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Weg fuer Kooperationen ausserhalb Europas (Kanada, Japan, Suedkorea, Singapur, Suedafrika u. a.). Deutschland nimmt nicht an jedem Globalstars-Call teil - die deutsche Beteiligung muss pro Call einzeln geprueft werden. Bei ZIM-Antragsstopp sind Antraege mit internationalen Partnern in offenen bi-/multilateralen Calls ausdruecklich ausgenommen - das macht diesen Weg 2026 fuer deutsche KMU besonders interessant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B - Offizielle Website (Eureka)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eurekanetwork.org/programmes-and-calls/globalstars/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">European Defence Fund (EDF) / EUDIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EU / Europaeische Kommission (DG DEFIS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuschuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUDIS zielt gezielt auf KMU, Start-ups und andere kleine Akteure, die neu im Verteidigungsbereich sind.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Actions: niedrigere TRL. Development Actions: hoehere TRL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDF-Regelfall: Konsortien aus mehreren Mitgliedstaaten. EUDIS enthaelt spezielle KMU-Calls mit niedrigeren Einstiegshuerden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Actions bis 4 Mio EUR, Development Actions bis 6 Mio EUR pro Projekt. EUDIS-Massnahmen machen ca. 23 % des EDF-Budgets 2026 aus (rund 231 Mio EUR).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Actions (fuer KMU und Forschungseinrichtungen) 100 %. Development Actions abweichend - im Call-Dokument pruefen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 bis 4 Jahre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDF-Calls 2026 schliessen am 29.09.2026, 17:00 Bruesseler Zeit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zusaetzlich zu Zuschuessen gibt es Business Coaching und einen Business Accelerator fuer europaeische Verteidigungs-Start-ups. Massgeblich ist das EDF Work Programme 2026 im Funding &amp; Tenders Portal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verteidigungsbezug ist zwingend - das ist eine strategische Positionierungsentscheidung, kein Nebenprojekt: sie beeinflusst Investorenkreis, Kundenstruktur und Exportkontrolle dauerhaft. Beachten Sie ausserdem: Eurostars, EIC Pathfinder, Transition und AIC sind strikt zivil, ein paralleler Verteidigungszweig kann dort Fragen aufwerfen.</t>
   </si>
   <si>
     <t xml:space="preserve">C - Sekundaerquelle, vor Antrag verifizieren</t>
   </si>
   <si>
-    <t xml:space="preserve">eurekanetwork.org/programmes-and-calls/eureka-clusters/xecs-call-6-2026/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eureka Globalstars / Network Projects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eureka-Netzwerk; Foerderung national</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMU, Grossunternehmen, Hochschulen, Forschungseinrichtungen, Non-Profits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottom-up, keine TRL-Vorgabe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mind. 2 voneinander unabhaengige Entitaeten; mind. 1 aus einem am Call teilnehmenden Eureka-Land und mind. 1 weitere unabhaengige aus dem jeweiligen Globalstars-Partnerland.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Call-abhaengig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rollierende bilaterale Calls; z. B. Canada Call for projects Nr. 7 mit Frist 27.08.2026. Aktuelle Calls unter eurekanetwork.org.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projekt muss auf Forschung/Entwicklung eines Produkts, Prozesses oder einer Dienstleistung gerichtet sein und ausschliesslich zivile, nicht-militaerische Anwendungen verfolgen. Kein einzelnes Unternehmen und kein einzelnes Land darf mehr als 70 % des Projektbudgets tragen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Der Weg fuer Kooperationen ausserhalb Europas (Kanada, Japan, Suedkorea, Singapur, Suedafrika u. a.). Deutschland nimmt nicht an jedem Globalstars-Call teil - die deutsche Beteiligung muss pro Call einzeln geprueft werden. Bei ZIM-Antragsstopp sind Antraege mit internationalen Partnern in offenen bi-/multilateralen Calls ausdruecklich ausgenommen - das macht diesen Weg 2026 fuer deutsche KMU besonders interessant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B - Offizielle Website (Eureka)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eurekanetwork.org/programmes-and-calls/globalstars/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">European Defence Fund (EDF) / EUDIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EU / Europaeische Kommission (DG DEFIS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zuschuss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUDIS zielt gezielt auf KMU, Start-ups und andere kleine Akteure, die neu im Verteidigungsbereich sind.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Actions: niedrigere TRL. Development Actions: hoehere TRL.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDF-Regelfall: Konsortien aus mehreren Mitgliedstaaten. EUDIS enthaelt spezielle KMU-Calls mit niedrigeren Einstiegshuerden.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Actions bis 4 Mio EUR, Development Actions bis 6 Mio EUR pro Projekt. EUDIS-Massnahmen machen ca. 23 % des EDF-Budgets 2026 aus (rund 231 Mio EUR).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Actions (fuer KMU und Forschungseinrichtungen) 100 %. Development Actions abweichend - im Call-Dokument pruefen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 bis 4 Jahre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDF-Calls 2026 schliessen am 29.09.2026, 17:00 Bruesseler Zeit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zusaetzlich zu Zuschuessen gibt es Business Coaching und einen Business Accelerator fuer europaeische Verteidigungs-Start-ups. Massgeblich ist das EDF Work Programme 2026 im Funding &amp; Tenders Portal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verteidigungsbezug ist zwingend - das ist eine strategische Positionierungsentscheidung, kein Nebenprojekt: sie beeinflusst Investorenkreis, Kundenstruktur und Exportkontrolle dauerhaft. Beachten Sie ausserdem: Eurostars, EIC Pathfinder, Transition und AIC sind strikt zivil, ein paralleler Verteidigungszweig kann dort Fragen aufwerfen.</t>
-  </si>
-  <si>
     <t xml:space="preserve">eudis.europa.eu/eudis-tracks/sme-calls_en</t>
   </si>
   <si>
@@ -818,7 +884,7 @@
     <t xml:space="preserve">Typisch 1 Jahr</t>
   </si>
   <si>
-    <t xml:space="preserve">Frist der Ausschreibung 2026 laut Sekundaerquelle 18.05.2026 - abgelaufen. Naechste Runde ueber eitdigital.eu verfolgen.</t>
+    <t xml:space="preserve">Frist der Ausschreibung 2026 laut der zitierten Sekundaerquelle 15.05.2026 - abgelaufen. Naechste Runde ueber eitdigital.eu verfolgen.</t>
   </si>
   <si>
     <t xml:space="preserve">Foerdert kollaborative Innovationsprojekte zur digitalen Transformation Europas - KI, Daten, Cybersicherheit. Zugang zum EIT-Digital-Netzwerk und Accelerator-Diensten ist oft wertvoller als der Zuschussbetrag selbst.</t>
@@ -857,7 +923,7 @@
     <t xml:space="preserve">Mehrjaehrig</t>
   </si>
   <si>
-    <t xml:space="preserve">Antraege bis 23.04.2026, 17:00 CET ueber das EU Funding &amp; Tenders Portal - abgelaufen. Naechste Runde beobachten.</t>
+    <t xml:space="preserve">Zwei verschiedene Fristen, keine gemeinsame: Net-Zero-Technologies-Zuschusscall bis 23.04.2026, 17:00 CET; die beiden Auktionen (Wasserstoff, industrielle Prozesswaerme) liefen bereits am 19.02.2026 aus. Beide abgelaufen - naechste Runde beobachten.</t>
   </si>
   <si>
     <t xml:space="preserve">Finanziert aus Erloesen des EU-Emissionshandels; geschaetztes Gesamtvolumen rund 40 Mrd EUR zwischen 2020 und 2030. Der Net-Zero-Technologies-Call deckt Dekarbonisierungsprojekte in Gross-, Mittel- und Kleinformat, Cleantech-Fertigung und Pilotprojekte ab.</t>
@@ -974,6 +1040,123 @@
     <t xml:space="preserve">Ein Seal ist kein Geld, sondern ein Tuerklopfer. Ob er in Deutschland tatsaechlich Mittel ausloest, haengt vom jeweiligen Bundesland und dessen EFRE-Programm ab und ist regional sehr unterschiedlich - vorab beim Land klaeren, sonst ist der Seal ein reiner Marketing-Titel.</t>
   </si>
   <si>
+    <t xml:space="preserve">ERC Proof of Concept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EU / European Research Council (ERCEA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuschuss, Pauschale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ausschliesslich bisherige oder laufende ERC-Grantees (Principal Investigators). Kein offener Wettbewerb.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verwertungspotenzial aus einem laufenden oder abgeschlossenen ERC-Projekt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einzelantrag ueber die Gasteinrichtung des PI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.000 EUR Pauschale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typisch 18 Monate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mehrere Cut-offs pro Jahr - aktuelle Termine im EU Funding &amp; Tenders Portal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nur zugaenglich, wenn ein ERC-Grant vorliegt. Aufgenommen, weil ERC PoC eines der foerderfaehigen Vorprojekte fuer EIC Transition ist - und die Liste sonst den Filter benennt, ohne einen Weg dorthin zu zeigen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuer Sie nur ueber das Gruendernetzwerk relevant: wer einen ERC-Grant an einer Hochschule hat, kann darueber den Zugang zu EIC Transition oeffnen. Betraege und Laufzeit vor Nutzung am aktuellen ERC Work Programme verifizieren - hier nicht aus der Primaerquelle geprueft.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">erc.europa.eu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSCA - Marie Sklodowska-Curie Actions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EU / Europaeische Kommission (REA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuschuss fuer Personalkosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unternehmen als Gastgeber oder Partner fuer Doktorandinnen und Postdocs (Doctoral Networks, Postdoctoral Fellowships, Staff Exchanges).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forschungsnah, unabhaengig vom TRL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctoral Networks: Konsortium. Postdoctoral Fellowships: Antrag von Forscherin/Forscher gemeinsam mit der Gasteinrichtung.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personalkostenpauschalen je Forscherjahr plus Zuschlaege - Saetze im jeweiligen Work Programme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 % ueber Einheitskostensaetze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fellowships typisch 1-2 Jahre, Netzwerke bis 4 Jahre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaehrliche Calls mit festen Fristen - Termine im EU Funding &amp; Tenders Portal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guenstigster Weg, Forschungskapazitaet und Hochschulanbindung ins Unternehmen zu holen, ohne die eigene Lohnsumme zu belasten. Fuer ein AI-Startup vor allem als Aufbau der wissenschaftlichen Substanz interessant, die spaeter fuer Pathfinder oder Eurostars gebraucht wird.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kein Projektzuschuss - es finanziert Koepfe, nicht Sachmittel oder Entwicklung. Konkrete Saetze und Fristen wurden hier NICHT aus der Primaerquelle geprueft; vor Planung am MSCA Work Programme verifizieren.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marie-sklodowska-curie-actions.ec.europa.eu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eureka Innowwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eureka-Netzwerk, ko-finanziert aus Horizon Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuschuss, Festbetrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einzelnes europaeisches KMU - kein Konsortium erforderlich.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Markt- und Machbarkeitsstudie vor einem groesseren Vorhaben.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kein Konsortium.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.000 EUR Festbetrag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Festbetrag (kein Prozentsatz).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typisch 6 Monate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rollierende Calls - Termine ueber eurekanetwork.org.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanziert eine Machbarkeitsstudie fuer Marktchancen ausserhalb Europas. Gleiche Plattform und gleiches Oekosystem wie Eurostars.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufwand vergleichbar mit EuroHPC, nicht mit Eurostars - deshalb ein sinnvoller Vorlauf, um einen internationalen Partner und einen Business Case zu belegen, bevor man einen vollen Eurostars- oder Globalstars-Antrag aufsetzt. Betrag und Laufzeit hier NICHT aus der Primaerquelle geprueft.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eurekanetwork.org/programmes-and-calls/innowwide/</t>
+  </si>
+  <si>
     <t xml:space="preserve">02 | Deutsche Bundesprogramme - kombinierbar mit EU-Foerderung - Stand 11.08.2026   (Passung: 5 = sehr gut  |  Aufwand: 1 = gering, 5 = sehr hoch)</t>
   </si>
   <si>
@@ -995,7 +1178,7 @@
     <t xml:space="preserve">Kein Konsortium noetig; Auftragsforschung und Kooperationen sind foerderfaehig.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ab 01.01.2026: Bemessungsgrundlage 12 Mio EUR pro Jahr. KMU-Satz 35 % ergibt bis zu 4,2 Mio EUR pro Jahr.</t>
+    <t xml:space="preserve">Ab 01.01.2026: Bemessungsgrundlage 12 Mio EUR pro Jahr (Paragraf 3 Abs. 5 Nr. 4 FZulG). KMU-Satz 35 % ergibt bis zu 4,2 Mio EUR pro Jahr. WICHTIG bei mehreren Firmen: nach Paragraf 3 Abs. 6 FZulG gilt die Grenze bei verbundenen Unternehmen fuer alle zusammen nur EINMAL - nicht je Gesellschaft. Zusaetzlich Deckel nach Paragraf 4 Abs. 3 FZulG: max. 15 Mio EUR Gesamtbeihilfe je Unternehmen und Vorhaben.</t>
   </si>
   <si>
     <t xml:space="preserve">25 % Grundsatz; 35 % fuer KMU (10 Prozentpunkte KMU-Bonus).</t>
@@ -1010,7 +1193,7 @@
     <t xml:space="preserve">Zweistufig: (1) Bescheinigung der Foerderfaehigkeit des Vorhabens bei der BSFZ; (2) Antrag auf Forschungszulage beim Finanzamt. Anrechnung auf die naechste Steuerfestsetzung; uebersteigt die Zulage die Steuerschuld, wird sie ausgezahlt.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kumulierungsregel beachten: Nach Paragraf 7 Abs. 1 FZulG kann die Forschungszulage grundsaetzlich auch dann in Anspruch genommen werden, wenn fuer dasselbe FuE-Vorhaben andere Foerderungen gewaehrt werden. ABER nach Paragraf 7 Abs. 2 Satz 2 FZulG duerfen Aufwendungen NICHT in die Bemessungsgrundlage einbezogen werden, soweit sie bereits im Rahmen anderer Foerderungen oder staatlicher Beihilfen beruecksichtigt wurden - und das gilt ausdruecklich auch fuer Foerderungen aus Unionsmitteln. Entscheidend ist nicht die Hoehe der anderen Foerderung, sondern die Kostenbasis. Praktische Konsequenz: pro Projekt und pro Kostenposition sauber trennen, welche Stunden in den EU-Zuschuss und welche in die Forschungszulage laufen. Bei Lump-Sum-Foerderungen (EIC) ist diese Abgrenzung besonders sorgfaeltig zu dokumentieren.</t>
+    <t xml:space="preserve">Kumulierungsregel beachten: Nach Paragraf 7 Abs. 1 FZulG kann die Forschungszulage grundsaetzlich auch dann in Anspruch genommen werden, wenn fuer dasselbe FuE-Vorhaben andere Foerderungen gewaehrt werden. ABER nach Paragraf 7 Abs. 2 SATZ 1 FZulG duerfen Aufwendungen NICHT in die Bemessungsgrundlage einbezogen werden, soweit sie bereits im Rahmen anderer Foerderungen oder staatlicher Beihilfen beruecksichtigt wurden; Satz 2 stellt klar, dass dies auch fuer Foerderungen aus Unionsmitteln gilt. Entscheidend ist nicht die Hoehe der anderen Foerderung, sondern die Kostenbasis. Praktische Konsequenz: pro Projekt und pro Kostenposition sauber trennen, welche Stunden in den EU-Zuschuss und welche in die Forschungszulage laufen. Bei Lump-Sum-Foerderungen (EIC) ist diese Abgrenzung besonders sorgfaeltig zu dokumentieren.</t>
   </si>
   <si>
     <t xml:space="preserve">A - Primaerquelle (FZulG, gesetze-im-internet.de) / B fuer Werte ab 2026</t>
@@ -1028,7 +1211,7 @@
     <t xml:space="preserve">Zuschuss (nicht rueckzahlbar)</t>
   </si>
   <si>
-    <t xml:space="preserve">KMU nach EU-Definition; kleine Unternehmen unter 50 MA nur in Kooperation mit KMU; mittlere Unternehmen unter 250 MA; weitere mittelstaendische Unternehmen unter 500 bzw. unter 1.000 MA - letztere nur in Kooperationsprojekten mit mindestens einem KMU. Forschungseinrichtungen als Partner.</t>
+    <t xml:space="preserve">KMU nach EU-Definition (Nr. 3.1.1 Buchst. a) - antragsberechtigt fuer Einzel- UND Kooperationsprojekte. Weitere mittelstaendische Unternehmen bis 499 MA (Buchst. b) ebenfalls fuer beides. Unternehmen bis 999 MA (Buchst. c) NUR in Kooperationsprojekten. Forschungseinrichtungen als Partner.</t>
   </si>
   <si>
     <t xml:space="preserve">Marktorientierte FuE bis zum Prototyp.</t>
@@ -1037,10 +1220,10 @@
     <t xml:space="preserve">Varianten: Einzelprojekt, Kooperationsprojekt KMU-KMU, KMU-Forschungseinrichtung, Netzwerkprojekt, internationale Kooperationsprojekte.</t>
   </si>
   <si>
-    <t xml:space="preserve">Je Unternehmen und Teilprojekt bis 560.000 EUR; Forschungseinrichtungen bis 280.000 EUR je Teilprojekt; Gesamtprojekt max. 3.000.000 EUR.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nationale Projekte: kleine Unternehmen in strukturschwachen Regionen 55 %, kleine junge Unternehmen 50 %, kleine Unternehmen 45 %, mittlere Unternehmen 40 %, weitere Mittelstaendler unter 500 MA 30 %, unter 1.000 MA mit KMU-Partner 30 %, Forschungseinrichtungen 100 %. Internationale Projekte erhalten 5 bis 10 Prozentpunkte mehr.</t>
+    <t xml:space="preserve">ACHTUNG - das sind ZUWENDUNGSFAEHIGE KOSTEN, nicht Foerderbetraege (Nr. 5.4.1): Einzelprojekt bis 690.000 EUR, Kooperationsprojekt bis 560.000 EUR je Unternehmen, Forschungseinrichtung bis 280.000 EUR. Der Zuschuss ergibt sich aus Kosten x Foerdersatz - ein kleines Unternehmen im Kooperationsprojekt erhaelt also max. 560.000 x 45 % = 252.000 EUR. Nur die Zuwendungshoehe fuer das Gesamt-Kooperationsprojekt ist echt gedeckelt: max. 3.000.000 EUR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drei getrennte Spalten (Nr. 5.2.1) - Einzelprojekt / Kooperation national / Kooperation mit auslaendischem Partner: kleine U. in strukturschwachen Regionen 45 / 55 / 60 %; kleine junge U. 45 / 50 / 60 %; kleine U. 40 / 45 / 55 %; mittlere U. 35 / 40 / 50 %; U. nach 3.1.1 b 25 / 30 / 40 %; U. nach 3.1.1 c kein Einzelprojekt / 30 / 40 %. Nichtwirtschaftliche Forschungseinrichtungen 100 %.</t>
   </si>
   <si>
     <t xml:space="preserve">Projektabhaengig, typisch 2-3 Jahre</t>
@@ -1049,16 +1232,16 @@
     <t xml:space="preserve">ACHTUNG: Seit 07.07.2026, 12:00 Uhr befristeter Antragsstopp. Aufhebung wird fuer Anfang 2027 angestrebt, ist aber ausdruecklich NICHT zugesichert und haengt vom Bundeshaushalt 2027 ab.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rechtsgrundlage ist die ZIM-Richtlinie V5 (Bundesanzeiger vom 01.11.2024, in Kraft seit 01.01.2025).</t>
+    <t xml:space="preserve">Rechtsgrundlage: Foerderrichtlinie Zentrales Innovationsprogramm Mittelstand vom 28.11.2024, veroeffentlicht BAnz AT 11.12.2024 B1, in Kraft seit 01.01.2025. Zusaetzliche Begrenzung nach Nr. 5.4.1: max. zwei bewilligte FuE-Projekte je Unternehmen innerhalb von zwoelf Monaten.</t>
   </si>
   <si>
     <t xml:space="preserve">Der Antragsstopp gilt fuer alle Projektformen und auch fuer Projektskizzen. AUSGENOMMEN sind Antraege mit internationalen Partnern innerhalb offener bi- und multilateraler Calls - das ist derzeit das einzige offene Tor und ein starkes Argument, ein Vorhaben international aufzusetzen (siehe Eurostars, Globalstars). Bereits eingereichte Antraege werden weiter bearbeitet, Auszahlungen fuer bewilligte Projekte laufen unveraendert.</t>
   </si>
   <si>
-    <t xml:space="preserve">A/B - Offizielle Website zim.de + Projekttraeger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zim.de/ZIM/Redaktion/DE/Meldungen/2026/3/2026-07-07-befristeter-antragsstopp.html</t>
+    <t xml:space="preserve">A - Primaerquelle (ZIM-Richtlinie, BAnz AT 11.12.2024 B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bundesanzeiger.de BAnz AT 11.12.2024 B1 | zim.de/ZIM/Redaktion/DE/Meldungen/2026/3/2026-07-07-befristeter-antragsstopp.html</t>
   </si>
   <si>
     <t xml:space="preserve">KMU-innovativ: IKT (inkl. Kuenstliche Intelligenz)</t>
@@ -1112,7 +1295,7 @@
     <t xml:space="preserve">Antragstellerin ist die Hochschule/Forschungseinrichtung, nicht das Team selbst.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lebensunterhalt: 3.000 EUR/Monat fuer Promovierte, 2.500 EUR fuer Hochschulabsolventen, 1.000 EUR fuer Studierende; Kinderzuschlag 150 EUR. Sachmittel bis 30.000 EUR bei Einzelgruendung bzw. bis 10.000 EUR je weiterer Person.</t>
+    <t xml:space="preserve">Lebensunterhalt: 3.000 EUR/Monat fuer Promovierte, 2.500 EUR fuer Hochschulabsolventen, 2.000 EUR fuer Gruendende mit Berufsabschluss, 1.000 EUR fuer Studierende; Kinderzuschlag 150 EUR. Sachmittel: 30.000 EUR fuer TEAMS, bis 10.000 EUR bei EINZELGRUENDUNG (in einer frueheren Fassung dieser Liste vertauscht). Zusaetzlich Coachingbudget 5.000 EUR.</t>
   </si>
   <si>
     <t xml:space="preserve">Stipendium, keine Quote.</t>
@@ -1148,13 +1331,13 @@
     <t xml:space="preserve">Phase I an der Hochschule/Forschungseinrichtung, Phase II im gegruendeten Unternehmen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase I: Personalstellen nach TV-L-Eingruppierung plus Sachmittel. Betraege sind vorhabensabhaengig.</t>
+    <t xml:space="preserve">Phase I: Personalstellen nach TV-L-Eingruppierung plus Sachausgaben bis 250.000 EUR. Phase II: bis 180.000 EUR.</t>
   </si>
   <si>
     <t xml:space="preserve">Phase I an Hochschulen i. d. R. Vollfinanzierung; Phase II anteilig.</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase I bis 18 Monate, Phase II bis 18 Monate (im Handbuch pruefen)</t>
+    <t xml:space="preserve">Phase I i. d. R. 18 Monate, Verlaengerung bis 36 Monate moeglich. Kein Direkteinstieg in Phase II (Ausnahme: KI-Modellprojekt aus dem Gruendungsstipendium).</t>
   </si>
   <si>
     <t xml:space="preserve">Laufende Antragstellung; Details im Handbuch EXIST-Forschungstransfer, 5. aktualisierte Auflage 2026.</t>
@@ -1184,25 +1367,25 @@
     <t xml:space="preserve">Fruehphase / Seed.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kein Konsortium.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erwerbszuschuss auf die Beteiligungssumme; zusaetzlich Exitzuschuss moeglich. Konkrete Saetze und Hoechstbetraege wurden nicht aus einer Primaerquelle verifiziert.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nach Sekundaerquellen 25 % Erwerbszuschuss - VOR Nutzung zwingend beim BAFA verifizieren.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laufend; Foerderfaehigkeit der Zielgesellschaft muss VOR Abschluss der Beteiligung bestaetigt sein.</t>
+    <t xml:space="preserve">Erwerbszuschuss 25 % der Beteiligungssumme, max. 100.000 EUR je Investor und Jahr (entspricht 666.666,66 EUR Investitionssumme). Zusaetzlich Exitzuschuss 25 % auf realisierte Veraeusserungsgewinne fuer natuerliche Personen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 % Erwerbszuschuss, steuerfrei.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEFRISTET BIS 31.12.2026 - danach ist eine Fortfuehrung offen. Antragstellung laufend, aber die Foerderfaehigkeit der Zielgesellschaft muss VOR Abschluss der Beteiligung bestaetigt sein.</t>
   </si>
   <si>
     <t xml:space="preserve">Bundesweites Foerderprogramm fuer Wagniskapital privater Investierender. Die Zielgesellschaft laesst sich vorab als foerderfaehig anerkennen, danach koennen Investoren den Zuschuss beantragen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Reihenfolge ist entscheidend: die Anerkennung der Zielgesellschaft muss VOR dem Beteiligungsvertrag vorliegen, sonst entfaellt der Zuschuss. Kein Geld fuer das Unternehmen direkt - der Hebel liegt darin, dass die Beteiligung fuer Angels attraktiver wird. Saetze und Konditionen wurden hier NICHT aus einer Primaerquelle bestaetigt - vor jeder Zusage an Investoren beim BAFA pruefen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bafa.de INVEST</t>
+    <t xml:space="preserve">Zwei K.-o.-Punkte: (1) Das Programm laeuft zum 31.12.2026 aus - wer den Hebel noch nutzen will, muss die Beteiligung bis dahin abgeschlossen haben. (2) Die Anerkennung der Zielgesellschaft muss VOR dem Beteiligungsvertrag vorliegen, sonst entfaellt der Zuschuss rueckwirkend. Kein Geld fuer das Unternehmen direkt - der Hebel liegt darin, dass die Beteiligung fuer Angels attraktiver wird.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B - Offizielle Website (BAFA/BMWE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bafa.de/DE/Wirtschaft/Beratung_Finanzierung/Invest/invest_node.html</t>
   </si>
   <si>
     <t xml:space="preserve">IGF - Industrielle Gemeinschaftsforschung</t>
@@ -1313,7 +1496,88 @@
     <t xml:space="preserve">foerderdatenbank.de</t>
   </si>
   <si>
-    <t xml:space="preserve">03 | Fristenkalender 2026 / 2027  -  Referenzdatum in Zelle B3 aendern, alle Berechnungen aktualisieren sich</t>
+    <t xml:space="preserve">SPRIND - Bundesagentur fuer Sprunginnovationen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bund / SPRIND GmbH (BMFTR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenges (vorkommerzielle Auftraege), Validierung, Beteiligungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teams, Start-ups, KMU, Forschende - auch aus dem europaeischen Ausland. Kein Konsortium noetig.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprunginnovation - hohes technisches Risiko, grosse Hebelwirkung. TRL-Spanne bewusst weit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einzelbewerbung moeglich; bei Challenges treten Teams gegeneinander an.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge-abhaengig und sehr hoch. Referenz: Challenge 'Next Frontier AI' mit 125 Mio EUR Gesamtvolumen, bis zu 26,5 Mio EUR je Team ueber drei Stufen (Stufe 1 bis 3 Mio, Stufe 2 weitere 8 Mio, Stufe 3 weitere 15,5 Mio).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bei Challenges kein klassischer Zuschuss mit Eigenanteil, sondern vorkommerzielle Beschaffung.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge-abhaengig; 'Next Frontier AI' laeuft ueber 24 Monate in drei Stufen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATUS 'Next Frontier AI': Einreichungsfrist war 01.06.2026, die zehn Teams wurden am 17.07.2026 ausgewaehlt (drei aus Deutschland, zwei UK, zwei Schweiz, zwei Frankreich, eines Italien) - dieser Wettbewerb ist fuer neue Bewerbungen geschlossen. Weitere und kommende Challenges laufend auf sprind.org.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPRIND arbeitet ausdruecklich nicht im klassischen Zuwendungsverfahren: Auswahl ueber Wettbewerb bzw. direkte Ansprache, deutlich schnellere Entscheidungen als bei BMFTR-Programmen, kein Konsortialzwang, keine Antragsfristen im ueblichen Sinn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In der ersten Fassung dieser Liste gefehlt - fuer ein deutsches Deep-Tech-/AI-Unternehmen die groesste Luecke. Aber: 'Next Frontier AI' ist bereits vergeben, und SPRIND finanziert nur sehr wenige, sehr grosse Wetten. Realistisch ist das kein planbarer Foerderweg, sondern eine Option, die man beobachtet und bei passender Challenge sofort zieht. Konkrete Konditionen kommender Challenges vorab pruefen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B - Offizielle Website und SPRIND-Pressemitteilung vom 17.07.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sprind.org/de/challenges | sprind.org Pressemitteilung Next Frontier AI 17.07.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KfW / ERP-Kreditprogramme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bund / KfW ueber die Hausbank (Durchleitung)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foerderdarlehen, teils mit Haftungsfreistellung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMU und mittelstaendische Unternehmen; einzelne Programme speziell fuer junge Unternehmen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unabhaengig vom TRL - finanziert Investitionen und Betriebsmittel, nicht Forschung im engeren Sinn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programmabhaengig; die Innovations- und Digitalisierungsprogramme bewegen sich im Millionenbereich je Vorhaben.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zinsverbilligtes Darlehen, kein Zuschuss - Rueckzahlung mit Zins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mehrjaehrige Laufzeiten mit tilgungsfreien Anlaufjahren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laufend, kein Call-Verfahren. Antrag immer VOR Vorhabensbeginn ueber die Hausbank.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waehrend des ZIM-Antragsstopps das groesste noch offene Bundesinstrument fuer die etablierten Mittelstandsfirmen. Kein Wettbewerbsverfahren, keine Gutachter, keine Frist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fremdkapital statt Zuschuss - es verbessert die Liquiditaet, nicht die Eigenkapitalquote, und die Hausbank muss mitziehen (Durchleitungsprinzip, teilweise mit Haftungsfreistellung). Konkrete Programme, Konditionen und Hoechstbetraege wurden hier NICHT im Detail recherchiert; vor Nutzung auf kfw.de bzw. mit der Hausbank klaeren.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C - nicht im Detail recherchiert, vor Nutzung verifizieren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kfw.de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03 | Fristenkalender 2026 / 2027 (kein Anspruch auf Vollstaendigkeit - monatliche EIC-Accelerator-Short-Proposal-Batches und viele Topic-Fristen sind nicht einzeln gelistet). Referenzdatum in B3 aendern, Berechnungen aktualisieren sich.</t>
   </si>
   <si>
     <t xml:space="preserve">Referenzdatum (heute):</t>
@@ -1340,6 +1604,18 @@
     <t xml:space="preserve">Tage bis Frist</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-02-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EU Innovation Fund - Auktionen (H2 / Prozesswaerme)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gebotsabgabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CINEA</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-02-26</t>
   </si>
   <si>
@@ -1382,16 +1658,13 @@
     <t xml:space="preserve">Vollantrag ueber Funding &amp; Tenders Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">CINEA</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-05-12</t>
   </si>
   <si>
     <t xml:space="preserve">Vollantrag, max. 22 Seiten, Konsortium mind. 3 Entitaeten</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-18</t>
+    <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
     <t xml:space="preserve">Antrag (Angabe aus Sekundaerquelle - verifizieren)</t>
@@ -1400,6 +1673,18 @@
     <t xml:space="preserve">grantedai.com</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPRIND Challenge - Next Frontier AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bewerbung; zehn Teams am 17.07.2026 ausgewaehlt - geschlossen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sprind.org</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
@@ -1412,100 +1697,127 @@
     <t xml:space="preserve">2026-08-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Eureka Globalstars - Canada Call 7</t>
+    <t xml:space="preserve">Eureka Network Projects - Canada Call 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antrag - ACHTUNG: nur Kanada ist teilnehmendes Land, fuer dt. Partner ohne eigene Foerderung wertlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIC Accelerator - Full Proposal Cut-off 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vollantrag; erste Bewertung von Dual-use-Antraegen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIC STEP Scale Up - Batch 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antrag inkl. Businessplan und Investoren-Pre-Commitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurostars 3 - Call 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vollantrag; foerderfaehiges Vorprojekt zwingend erforderlich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">European Defence Fund (EDF) 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUDIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Europe Programme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diverse Topic-Fristen - topic-genau im Funding &amp; Tenders Portal pruefen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HaDEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMU-innovativ: IKT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projektskizze zum Stichtag (Angabe aus Sekundaerquelle - verifizieren)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMFTR / VDI-VDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIC Pathfinder Challenges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vollantrag, max. 30 Seiten - inkl. Challenge 'DeepRAP / trustworthy Cognitive AI'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antrag (Equity 10-30 Mio EUR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eureka Cluster ITEA 4 - Call 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Outline (PO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itea4.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIC Accelerator - Full Proposal Cut-off 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letzter Vollantrags-Cut-off 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIC STEP Scale Up - Batch 4</t>
   </si>
   <si>
     <t xml:space="preserve">Antrag</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIC Accelerator - Full Proposal Cut-off 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vollantrag; erste Bewertung von Dual-use-Antraegen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIC STEP Scale Up - Batch 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antrag inkl. Businessplan und Investoren-Pre-Commitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurostars 3 - Call 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vollantrag; foerderfaehiges Vorprojekt zwingend erforderlich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">European Defence Fund (EDF) 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUDIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMU-innovativ: IKT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projektskizze zum Stichtag (Angabe aus Sekundaerquelle - verifizieren)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMFTR / VDI-VDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIC Pathfinder Challenges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vollantrag, max. 30 Seiten - inkl. Challenge 'DeepRAP / trustworthy Cognitive AI'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antrag (Equity 10-30 Mio EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eureka Cluster ITEA 4 - Call 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Outline (PO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">itea4.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIC Accelerator - Full Proposal Cut-off 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Letzter Vollantrags-Cut-off 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIC STEP Scale Up - Batch 4</t>
+    <t xml:space="preserve">2027-01-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eureka Cluster Xecs - Call 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Outline - Deutschland ist kein teilnehmendes Land</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eurekanetwork.org</t>
   </si>
   <si>
     <t xml:space="preserve">2027-02-11</t>
@@ -1577,7 +1889,7 @@
     <t xml:space="preserve">EIC Accelerator ist der groesste Einzeltopf (bis 2,5 Mio Zuschuss plus 1-10 Mio Eigenkapital) und 2026 deutlich schneller. Aber: nach drei erfolglosen Einreichungen sind Sie bis Ende Horizon Europe gesperrt. Nicht als Experiment einreichen. Voraussetzung ist TRL 5 vollstaendig abgeschlossen und der Nachweis, dass Sie die 30 % Eigenanteil stemmen koennen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pathfinder Challenge 'DeepRAP - trustworthy Cognitive AI' ist der einzige explizit auf KI zugeschnittene EIC-Forschungstopf 2026: bis 4 Mio EUR bei 100 % Foerderquote, Frist 28.10.2026. Einzelantraege sind hier ausdruecklich zugelassen. Nur sinnvoll bei echtem Forschungsanteil Richtung TRL 3-4 - und die Auswahl folgt einer Portfolio-Logik, nicht nur dem Score.</t>
+    <t xml:space="preserve">Pathfinder Challenge 'DeepRAP - trustworthy Cognitive AI' ist der einzige explizit auf KI zugeschnittene PATHFINDER-Topf 2026 (der zweite KI-Topf im EIC ist die AIC-Challenge Physical AI, deren Stage 1 aber bereits ausgelaufen ist): bis 4 Mio EUR bei 100 % Foerderquote, Frist 28.10.2026. Einzelantraege sind hier ausdruecklich zugelassen. Nur sinnvoll bei echtem Forschungsanteil Richtung TRL 3-4 - und die Auswahl folgt einer Portfolio-Logik, nicht nur dem Score.</t>
   </si>
   <si>
     <t xml:space="preserve">KMU-innovativ IKT deckt KI-Vorhaben explizit ab, bis 50 % fuer Unternehmen und bis 100 % fuer Hochschulpartner. Das ist der naheliegende nationale Ersatz, solange ZIM gestoppt ist. Stichtag und Quoten stammen aus Sekundaerquellen - vor der Planung an der BMFTR-Bekanntmachung verifizieren.</t>
@@ -1598,7 +1910,13 @@
     <t xml:space="preserve">Landesprogramme wurden bewusst nicht recherchiert, weil das Bundesland Ihrer Firmen nicht bekannt ist. Sobald das feststeht, ist das der Bereich mit dem besten Aufwand-Nutzen-Verhaeltnis nach der Forschungszulage - und die Stelle, an der ein EIC Seal in Geld umgesetzt wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">Globalstars/Network Projects ist der Weg fuer Partner ausserhalb Europas (Kanada, Japan, Suedkorea, Singapur). Deutschland nimmt nicht an jedem Call teil - pro Call einzeln pruefen. Als international aufgesetztes Vorhaben faellt es zudem unter die ZIM-Ausnahme vom Antragsstopp.</t>
+    <t xml:space="preserve">SPRIND ist der groesste denkbare Einzelhebel in Deutschland - die Challenge 'Next Frontier AI' war mit 125 Mio EUR und bis zu 26,5 Mio EUR je Team dotiert. Aber genau diese Challenge ist seit dem 17.07.2026 vergeben, und SPRIND finanziert generell nur sehr wenige, sehr grosse Wetten. Deshalb: beobachten und bei passender kommender Challenge sofort ziehen - aber nichts darauf planen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innowwide ist der guenstigste Einstieg ins Eureka-Oekosystem: 60.000 EUR Festbetrag, ein einzelnes KMU, kein Konsortium. Sinnvoll als Vorlauf, um internationalen Partner und Business Case zu belegen, bevor Sie einen vollen Eurostars-Antrag aufsetzen. Konditionen vorab verifizieren.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Globalstars/Network Projects ist der Weg fuer Partner ausserhalb Europas (Kanada, Japan, Suedkorea, Singapur). Deutschland nimmt nicht an jedem Call teil - pro Call einzeln pruefen. Als international aufgesetztes Vorhaben faellt es zudem unter die ZIM-Ausnahme vom Antragsstopp. Achtung: der prominent gelistete Canada Call 7 fuehrt nur Kanada als teilnehmendes Land - fuer deutsche Partner ohne eigene Foerderung wertlos.</t>
   </si>
   <si>
     <t xml:space="preserve">Hinweis</t>
@@ -1619,7 +1937,7 @@
     <t xml:space="preserve">URL</t>
   </si>
   <si>
-    <t xml:space="preserve">EIC Work Programme 2026 (Annex C(2026) 4080), 209 Seiten</t>
+    <t xml:space="preserve">EIC Work Programme 2026, 2. Aenderung, angenommen 17.06.2026 (Annex C(2026) 4080), 209 Seiten</t>
   </si>
   <si>
     <t xml:space="preserve">A - Primaerquelle (PDF, Volltext ausgewertet)</t>
@@ -1806,6 +2124,57 @@
   </si>
   <si>
     <t xml:space="preserve">https://exist.de/wp-content/uploads/2024/10/260609_Handbuch_EFT_2026_barrierefrei.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZIM-Foerderrichtlinie vom 28.11.2024, BAnz AT 11.12.2024 B1, 29 Seiten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZIM Nr. 5.2.1 Foerdersaetze (drei Spalten), Nr. 5.4.1 zuwendungsfaehige Kosten 690.000 / 560.000 / 280.000 EUR und Zuwendungsdeckel 3.000.000 EUR, Nr. 3.1.1 Antragsberechtigte, Begrenzung auf zwei Bewilligungen in zwoelf Monaten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bundesanzeiger.de/pub/publication/H4hLAtOVVOn1N7yG6vR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FZulG Paragraf 3 (Bemessungsgrundlage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Mio EUR ab 2026 (Abs. 5 Nr. 4) und die Regel, dass die Grenze bei verbundenen Unternehmen nur einmal insgesamt gilt (Abs. 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.gesetze-im-internet.de/fzulg/__3.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAFA - INVEST Zuschuss fuer Wagniskapital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 % Erwerbszuschuss, max. 100.000 EUR je Investor und Jahr, Exitzuschuss, Befristung bis 31.12.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bafa.de/DE/Wirtschaft/Beratung_Finanzierung/Invest/invest_node.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPRIND - Next Frontier AI Challenge und Pressemitteilung vom 17.07.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B - Offizielle Website und Pressemitteilung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125 Mio EUR Gesamtvolumen, bis 26,5 Mio EUR je Team, Dreistufigkeit 3 / 8 / 15,5 Mio, Auswahl der zehn Teams am 17.07.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sprind.org/en/actions/challenges/next-frontier-ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eureka - Xecs Call 6 (Laenderliste und Fristen geprueft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B - Offizielle Call-Seite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deutschland nicht unter den teilnehmenden Laendern; Call-Oeffnung 23.06.2026, Project Outline 21.01.2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.eurekanetwork.org/programmes-and-calls/eureka-clusters/xecs-call-6-2026/</t>
   </si>
   <si>
     <t xml:space="preserve">Diverse Sekundaerquellen (Beratungsportale)</t>
@@ -2558,7 +2927,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C33"/>
+  <dimension ref="B1:C45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2720,15 +3089,15 @@
       </c>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
+    <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
         <v>37</v>
       </c>
@@ -2752,26 +3121,112 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="12" t="s">
+    <row r="31" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C31" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="13" t="n">
         <f aca="false">COUNTA(01_EU_Programme!B3:B100)+COUNTA(02_DE_Programme!B3:B100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="13" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="13" t="n">
         <f aca="false">COUNTIF(01_EU_Programme!P3:P100,"A*")+COUNTIF(02_DE_Programme!P3:P100,"A*")</f>
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:C4"/>
@@ -2779,6 +3234,7 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2796,7 +3252,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2819,7 +3275,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -2840,55 +3296,55 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2896,40 +3352,40 @@
         <v>1</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="N3" s="19" t="n">
         <v>5</v>
@@ -2938,10 +3394,10 @@
         <v>3</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="Q3" s="18" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2949,40 +3405,40 @@
         <v>2</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="M4" s="24" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="N4" s="20" t="n">
         <v>3</v>
@@ -2991,51 +3447,51 @@
         <v>4</v>
       </c>
       <c r="P4" s="21" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="N5" s="19" t="n">
         <v>4</v>
@@ -3044,51 +3500,51 @@
         <v>4</v>
       </c>
       <c r="P5" s="21" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q5" s="18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="282" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="N6" s="20" t="n">
         <v>3</v>
@@ -3097,10 +3553,10 @@
         <v>3</v>
       </c>
       <c r="P6" s="21" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="166.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3108,40 +3564,40 @@
         <v>5</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="N7" s="19" t="n">
         <v>5</v>
@@ -3150,10 +3606,10 @@
         <v>5</v>
       </c>
       <c r="P7" s="21" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q7" s="18" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3161,40 +3617,40 @@
         <v>6</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="N8" s="20" t="n">
         <v>3</v>
@@ -3203,10 +3659,10 @@
         <v>5</v>
       </c>
       <c r="P8" s="21" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q8" s="24" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3214,40 +3670,40 @@
         <v>7</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="N9" s="25" t="n">
         <v>2</v>
@@ -3256,10 +3712,10 @@
         <v>4</v>
       </c>
       <c r="P9" s="21" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q9" s="18" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3267,40 +3723,40 @@
         <v>8</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="N10" s="25" t="n">
         <v>1</v>
@@ -3309,10 +3765,10 @@
         <v>4</v>
       </c>
       <c r="P10" s="21" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3320,40 +3776,40 @@
         <v>9</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="N11" s="25" t="n">
         <v>2</v>
@@ -3362,51 +3818,51 @@
         <v>2</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q11" s="18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="M12" s="24" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="N12" s="20" t="n">
         <v>3</v>
@@ -3415,10 +3871,10 @@
         <v>5</v>
       </c>
       <c r="P12" s="26" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3426,40 +3882,40 @@
         <v>11</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="N13" s="20" t="n">
         <v>3</v>
@@ -3468,10 +3924,10 @@
         <v>4</v>
       </c>
       <c r="P13" s="26" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="Q13" s="18" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3479,40 +3935,40 @@
         <v>12</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="L14" s="24" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="M14" s="24" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="N14" s="19" t="n">
         <v>5</v>
@@ -3521,10 +3977,10 @@
         <v>1</v>
       </c>
       <c r="P14" s="26" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="Q14" s="24" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3532,40 +3988,40 @@
         <v>13</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="C15" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J15" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>188</v>
-      </c>
       <c r="K15" s="18" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="N15" s="20" t="n">
         <v>3</v>
@@ -3574,104 +4030,104 @@
         <v>4</v>
       </c>
       <c r="P15" s="26" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="Q15" s="18" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="J16" s="24" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="M16" s="24" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="N16" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="P16" s="27" t="s">
-        <v>228</v>
+      <c r="P16" s="26" t="s">
+        <v>249</v>
       </c>
       <c r="Q16" s="24" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="M17" s="18" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="N17" s="20" t="n">
         <v>3</v>
@@ -3680,10 +4136,10 @@
         <v>3</v>
       </c>
       <c r="P17" s="26" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="Q17" s="18" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3691,40 +4147,40 @@
         <v>16</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="J18" s="24" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="N18" s="25" t="n">
         <v>2</v>
@@ -3733,10 +4189,10 @@
         <v>4</v>
       </c>
       <c r="P18" s="27" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="Q18" s="24" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3744,40 +4200,40 @@
         <v>17</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="M19" s="18" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="N19" s="25" t="n">
         <v>2</v>
@@ -3786,51 +4242,51 @@
         <v>3</v>
       </c>
       <c r="P19" s="27" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="Q19" s="18" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="J20" s="24" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="L20" s="24" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="M20" s="24" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="N20" s="25" t="n">
         <v>1</v>
@@ -3839,10 +4295,10 @@
         <v>5</v>
       </c>
       <c r="P20" s="26" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="Q20" s="24" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3850,40 +4306,40 @@
         <v>19</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="M21" s="18" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="N21" s="25" t="n">
         <v>2</v>
@@ -3892,10 +4348,10 @@
         <v>3</v>
       </c>
       <c r="P21" s="26" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="Q21" s="18" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3903,40 +4359,40 @@
         <v>20</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="J22" s="24" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="L22" s="24" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="N22" s="25" t="n">
         <v>1</v>
@@ -3945,10 +4401,10 @@
         <v>1</v>
       </c>
       <c r="P22" s="21" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="Q22" s="24" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3956,40 +4412,40 @@
         <v>21</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="M23" s="18" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="N23" s="20" t="n">
         <v>3</v>
@@ -3998,14 +4454,173 @@
         <v>1</v>
       </c>
       <c r="P23" s="21" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="Q23" s="18" t="s">
-        <v>90</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>338</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="K24" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="L24" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="M24" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="N24" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P24" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q24" s="24" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="M25" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="N25" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q25" s="18" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="I26" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="J26" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="K26" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="L26" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="M26" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="N26" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q26" s="24" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q23"/>
+  <autoFilter ref="A2:Q26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -4026,7 +4641,7 @@
     <tabColor rgb="FF375623"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -4049,7 +4664,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>314</v>
+        <v>375</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -4070,55 +4685,55 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4126,40 +4741,40 @@
         <v>1</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>316</v>
+        <v>377</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>319</v>
+        <v>380</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>320</v>
+        <v>381</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>321</v>
+        <v>382</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>322</v>
+        <v>383</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>323</v>
+        <v>384</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>324</v>
+        <v>385</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>325</v>
+        <v>386</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>326</v>
+        <v>387</v>
       </c>
       <c r="N3" s="19" t="n">
         <v>5</v>
@@ -4168,51 +4783,51 @@
         <v>2</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="Q3" s="18" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="166.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>329</v>
+        <v>390</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>330</v>
+        <v>391</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>331</v>
+        <v>392</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>332</v>
+        <v>393</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>333</v>
+        <v>394</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>334</v>
+        <v>395</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>335</v>
+        <v>396</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>336</v>
+        <v>397</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>337</v>
+        <v>398</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>338</v>
+        <v>399</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>339</v>
+        <v>400</v>
       </c>
       <c r="M4" s="24" t="s">
-        <v>340</v>
+        <v>401</v>
       </c>
       <c r="N4" s="20" t="n">
         <v>3</v>
@@ -4221,10 +4836,10 @@
         <v>2</v>
       </c>
       <c r="P4" s="21" t="s">
-        <v>341</v>
+        <v>402</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>342</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4232,40 +4847,40 @@
         <v>3</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>343</v>
+        <v>404</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>344</v>
+        <v>405</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>345</v>
+        <v>406</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>346</v>
+        <v>407</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>347</v>
+        <v>408</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>349</v>
+        <v>410</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>350</v>
+        <v>411</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>351</v>
+        <v>412</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>352</v>
+        <v>413</v>
       </c>
       <c r="N5" s="19" t="n">
         <v>4</v>
@@ -4274,51 +4889,51 @@
         <v>3</v>
       </c>
       <c r="P5" s="27" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="Q5" s="18" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>354</v>
+        <v>415</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>355</v>
+        <v>416</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>356</v>
+        <v>417</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>357</v>
+        <v>418</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>358</v>
+        <v>419</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>360</v>
+        <v>421</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>362</v>
+        <v>423</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>363</v>
+        <v>424</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>364</v>
+        <v>425</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>365</v>
+        <v>426</v>
       </c>
       <c r="N6" s="25" t="n">
         <v>2</v>
@@ -4327,51 +4942,51 @@
         <v>2</v>
       </c>
       <c r="P6" s="27" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>367</v>
+        <v>428</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>355</v>
+        <v>416</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>368</v>
+        <v>429</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>369</v>
+        <v>430</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>370</v>
+        <v>431</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>371</v>
+        <v>432</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>372</v>
+        <v>433</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>373</v>
+        <v>434</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>374</v>
+        <v>435</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>375</v>
+        <v>436</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>377</v>
+        <v>438</v>
       </c>
       <c r="N7" s="25" t="n">
         <v>2</v>
@@ -4380,10 +4995,10 @@
         <v>3</v>
       </c>
       <c r="P7" s="27" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="Q7" s="18" t="s">
-        <v>378</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4391,40 +5006,40 @@
         <v>6</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>379</v>
+        <v>440</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>380</v>
+        <v>441</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>381</v>
+        <v>442</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>382</v>
+        <v>443</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>383</v>
+        <v>444</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>387</v>
+        <v>447</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>388</v>
+        <v>448</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>389</v>
+        <v>449</v>
       </c>
       <c r="N8" s="20" t="n">
         <v>3</v>
@@ -4432,11 +5047,11 @@
       <c r="O8" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="P8" s="27" t="s">
-        <v>228</v>
+      <c r="P8" s="26" t="s">
+        <v>450</v>
       </c>
       <c r="Q8" s="24" t="s">
-        <v>390</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4444,40 +5059,40 @@
         <v>7</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>391</v>
+        <v>452</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>392</v>
+        <v>453</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>393</v>
+        <v>454</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>394</v>
+        <v>455</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>395</v>
+        <v>456</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>396</v>
+        <v>457</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>397</v>
+        <v>458</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>398</v>
+        <v>459</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>399</v>
+        <v>460</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>400</v>
+        <v>461</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>401</v>
+        <v>462</v>
       </c>
       <c r="N9" s="25" t="n">
         <v>1</v>
@@ -4486,10 +5101,10 @@
         <v>2</v>
       </c>
       <c r="P9" s="27" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="Q9" s="18" t="s">
-        <v>402</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4497,40 +5112,40 @@
         <v>8</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>403</v>
+        <v>464</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>404</v>
+        <v>465</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>405</v>
+        <v>466</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>406</v>
+        <v>467</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>407</v>
+        <v>468</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>408</v>
+        <v>469</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>409</v>
+        <v>470</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>410</v>
+        <v>471</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>411</v>
+        <v>472</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>412</v>
+        <v>473</v>
       </c>
       <c r="N10" s="20" t="n">
         <v>3</v>
@@ -4539,10 +5154,10 @@
         <v>2</v>
       </c>
       <c r="P10" s="27" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>413</v>
+        <v>474</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4550,40 +5165,40 @@
         <v>9</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>414</v>
+        <v>475</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>415</v>
+        <v>476</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>416</v>
+        <v>477</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>417</v>
+        <v>478</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>418</v>
+        <v>479</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>419</v>
+        <v>480</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>420</v>
+        <v>481</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>421</v>
+        <v>482</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>421</v>
+        <v>482</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>422</v>
+        <v>483</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>423</v>
+        <v>484</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>424</v>
+        <v>485</v>
       </c>
       <c r="N11" s="20" t="n">
         <v>3</v>
@@ -4592,14 +5207,120 @@
         <v>2</v>
       </c>
       <c r="P11" s="27" t="s">
-        <v>425</v>
+        <v>486</v>
       </c>
       <c r="Q11" s="18" t="s">
-        <v>426</v>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>488</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>491</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>492</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>495</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>497</v>
+      </c>
+      <c r="L12" s="24" t="s">
+        <v>498</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>499</v>
+      </c>
+      <c r="N12" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" s="26" t="s">
+        <v>500</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>503</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>504</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>505</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>506</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>507</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>508</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>509</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>510</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>511</v>
+      </c>
+      <c r="M13" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="N13" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" s="27" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q13" s="18" t="s">
+        <v>514</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q11"/>
+  <autoFilter ref="A2:Q13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -4620,7 +5341,7 @@
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="13"/>
@@ -4633,7 +5354,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>427</v>
+        <v>515</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -4644,50 +5365,50 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>428</v>
+        <v>516</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>429</v>
+        <v>517</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>430</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>431</v>
+        <v>519</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>432</v>
+        <v>520</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>433</v>
+        <v>521</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>434</v>
+        <v>522</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>435</v>
+        <v>523</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>436</v>
+        <v>524</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>437</v>
+        <v>173</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>438</v>
+        <v>525</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E6" s="22" t="str">
         <f aca="false">IF(DATEVALUE(A6)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4695,24 +5416,24 @@
       </c>
       <c r="F6" s="30" t="n">
         <f aca="false">DATEVALUE(A6)-DATEVALUE($B$3)</f>
-        <v>-166</v>
+        <v>-173</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>440</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>442</v>
+        <v>529</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>443</v>
+        <v>530</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>444</v>
+        <v>531</v>
       </c>
       <c r="E7" s="16" t="str">
         <f aca="false">IF(DATEVALUE(A7)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4720,24 +5441,24 @@
       </c>
       <c r="F7" s="31" t="n">
         <f aca="false">DATEVALUE(A7)-DATEVALUE($B$3)</f>
-        <v>-145</v>
+        <v>-166</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>445</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>446</v>
+        <v>533</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>447</v>
+        <v>534</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>448</v>
+        <v>535</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>449</v>
+        <v>536</v>
       </c>
       <c r="E8" s="22" t="str">
         <f aca="false">IF(DATEVALUE(A8)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4745,24 +5466,24 @@
       </c>
       <c r="F8" s="30" t="n">
         <f aca="false">DATEVALUE(A8)-DATEVALUE($B$3)</f>
-        <v>-110</v>
+        <v>-145</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>450</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>451</v>
+        <v>538</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>437</v>
+        <v>539</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>77</v>
+        <v>540</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>452</v>
+        <v>541</v>
       </c>
       <c r="E9" s="16" t="str">
         <f aca="false">IF(DATEVALUE(A9)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4770,24 +5491,24 @@
       </c>
       <c r="F9" s="31" t="n">
         <f aca="false">DATEVALUE(A9)-DATEVALUE($B$3)</f>
-        <v>-91</v>
+        <v>-110</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>440</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>453</v>
+        <v>542</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>152</v>
+        <v>529</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>254</v>
+        <v>98</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>454</v>
+        <v>543</v>
       </c>
       <c r="E10" s="22" t="str">
         <f aca="false">IF(DATEVALUE(A10)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4795,24 +5516,24 @@
       </c>
       <c r="F10" s="30" t="n">
         <f aca="false">DATEVALUE(A10)-DATEVALUE($B$3)</f>
-        <v>-85</v>
+        <v>-91</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>455</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>456</v>
+        <v>544</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>437</v>
+        <v>173</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>457</v>
+        <v>276</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>458</v>
+        <v>545</v>
       </c>
       <c r="E11" s="16" t="str">
         <f aca="false">IF(DATEVALUE(A11)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4820,74 +5541,74 @@
       </c>
       <c r="F11" s="31" t="n">
         <f aca="false">DATEVALUE(A11)-DATEVALUE($B$3)</f>
-        <v>-34</v>
+        <v>-88</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>440</v>
+        <v>546</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>459</v>
+        <v>547</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>460</v>
+        <v>548</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>461</v>
+        <v>549</v>
       </c>
       <c r="E12" s="22" t="str">
         <f aca="false">IF(DATEVALUE(A12)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
-        <v>offen</v>
+        <v>abgelaufen</v>
       </c>
       <c r="F12" s="30" t="n">
         <f aca="false">DATEVALUE(A12)-DATEVALUE($B$3)</f>
-        <v>16</v>
+        <v>-71</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>445</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>462</v>
+        <v>551</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>437</v>
+        <v>529</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>463</v>
+        <v>552</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>464</v>
+        <v>553</v>
       </c>
       <c r="E13" s="16" t="str">
         <f aca="false">IF(DATEVALUE(A13)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
-        <v>offen</v>
+        <v>abgelaufen</v>
       </c>
       <c r="F13" s="31" t="n">
         <f aca="false">DATEVALUE(A13)-DATEVALUE($B$3)</f>
-        <v>22</v>
+        <v>-34</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>465</v>
+        <v>554</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>437</v>
+        <v>173</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>466</v>
+        <v>555</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>467</v>
+        <v>556</v>
       </c>
       <c r="E14" s="22" t="str">
         <f aca="false">IF(DATEVALUE(A14)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4895,24 +5616,24 @@
       </c>
       <c r="F14" s="30" t="n">
         <f aca="false">DATEVALUE(A14)-DATEVALUE($B$3)</f>
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>440</v>
+        <v>537</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>468</v>
+        <v>557</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>442</v>
+        <v>529</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>469</v>
+        <v>558</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>444</v>
+        <v>559</v>
       </c>
       <c r="E15" s="16" t="str">
         <f aca="false">IF(DATEVALUE(A15)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4920,24 +5641,24 @@
       </c>
       <c r="F15" s="31" t="n">
         <f aca="false">DATEVALUE(A15)-DATEVALUE($B$3)</f>
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>445</v>
+        <v>532</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>470</v>
+        <v>560</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>437</v>
+        <v>529</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>102</v>
+        <v>561</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>471</v>
+        <v>562</v>
       </c>
       <c r="E16" s="22" t="str">
         <f aca="false">IF(DATEVALUE(A16)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4945,24 +5666,24 @@
       </c>
       <c r="F16" s="30" t="n">
         <f aca="false">DATEVALUE(A16)-DATEVALUE($B$3)</f>
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>472</v>
+        <v>563</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>437</v>
+        <v>534</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>473</v>
+        <v>564</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>449</v>
+        <v>536</v>
       </c>
       <c r="E17" s="16" t="str">
         <f aca="false">IF(DATEVALUE(A17)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4970,24 +5691,24 @@
       </c>
       <c r="F17" s="31" t="n">
         <f aca="false">DATEVALUE(A17)-DATEVALUE($B$3)</f>
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>474</v>
+        <v>537</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>475</v>
+        <v>565</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>152</v>
+        <v>529</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>476</v>
+        <v>123</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>477</v>
+        <v>566</v>
       </c>
       <c r="E18" s="22" t="str">
         <f aca="false">IF(DATEVALUE(A18)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -4995,24 +5716,24 @@
       </c>
       <c r="F18" s="30" t="n">
         <f aca="false">DATEVALUE(A18)-DATEVALUE($B$3)</f>
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>478</v>
+        <v>532</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>479</v>
+        <v>567</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>437</v>
+        <v>529</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>480</v>
+        <v>568</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>481</v>
+        <v>541</v>
       </c>
       <c r="E19" s="16" t="str">
         <f aca="false">IF(DATEVALUE(A19)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -5020,24 +5741,24 @@
       </c>
       <c r="F19" s="31" t="n">
         <f aca="false">DATEVALUE(A19)-DATEVALUE($B$3)</f>
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>440</v>
+        <v>569</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>479</v>
+        <v>570</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>437</v>
+        <v>173</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>146</v>
+        <v>571</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>482</v>
+        <v>572</v>
       </c>
       <c r="E20" s="22" t="str">
         <f aca="false">IF(DATEVALUE(A20)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -5045,24 +5766,24 @@
       </c>
       <c r="F20" s="30" t="n">
         <f aca="false">DATEVALUE(A20)-DATEVALUE($B$3)</f>
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>440</v>
+        <v>573</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>483</v>
+        <v>574</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>447</v>
+        <v>173</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>484</v>
+        <v>575</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>485</v>
+        <v>576</v>
       </c>
       <c r="E21" s="16" t="str">
         <f aca="false">IF(DATEVALUE(A21)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -5070,24 +5791,24 @@
       </c>
       <c r="F21" s="31" t="n">
         <f aca="false">DATEVALUE(A21)-DATEVALUE($B$3)</f>
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>486</v>
+        <v>577</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
-        <v>487</v>
+        <v>578</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>437</v>
+        <v>529</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>488</v>
+        <v>579</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>489</v>
+        <v>580</v>
       </c>
       <c r="E22" s="22" t="str">
         <f aca="false">IF(DATEVALUE(A22)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -5095,24 +5816,24 @@
       </c>
       <c r="F22" s="30" t="n">
         <f aca="false">DATEVALUE(A22)-DATEVALUE($B$3)</f>
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>490</v>
+        <v>578</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>437</v>
+        <v>529</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>491</v>
+        <v>167</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>461</v>
+        <v>581</v>
       </c>
       <c r="E23" s="16" t="str">
         <f aca="false">IF(DATEVALUE(A23)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -5120,24 +5841,24 @@
       </c>
       <c r="F23" s="31" t="n">
         <f aca="false">DATEVALUE(A23)-DATEVALUE($B$3)</f>
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>492</v>
+        <v>582</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>447</v>
+        <v>539</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>484</v>
+        <v>583</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>493</v>
+        <v>584</v>
       </c>
       <c r="E24" s="22" t="str">
         <f aca="false">IF(DATEVALUE(A24)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -5145,24 +5866,24 @@
       </c>
       <c r="F24" s="30" t="n">
         <f aca="false">DATEVALUE(A24)-DATEVALUE($B$3)</f>
-        <v>184</v>
+        <v>83</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>486</v>
+        <v>585</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>494</v>
+        <v>586</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>437</v>
+        <v>529</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>495</v>
+        <v>587</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>496</v>
+        <v>588</v>
       </c>
       <c r="E25" s="16" t="str">
         <f aca="false">IF(DATEVALUE(A25)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
@@ -5170,32 +5891,132 @@
       </c>
       <c r="F25" s="31" t="n">
         <f aca="false">DATEVALUE(A25)-DATEVALUE($B$3)</f>
+        <v>85</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22" t="s">
+        <v>589</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>529</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>590</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>591</v>
+      </c>
+      <c r="E26" s="22" t="str">
+        <f aca="false">IF(DATEVALUE(A26)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
+        <v>offen</v>
+      </c>
+      <c r="F26" s="30" t="n">
+        <f aca="false">DATEVALUE(A26)-DATEVALUE($B$3)</f>
+        <v>106</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>594</v>
+      </c>
+      <c r="E27" s="16" t="str">
+        <f aca="false">IF(DATEVALUE(A27)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
+        <v>offen</v>
+      </c>
+      <c r="F27" s="31" t="n">
+        <f aca="false">DATEVALUE(A27)-DATEVALUE($B$3)</f>
+        <v>163</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22" t="s">
+        <v>596</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>539</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>583</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="E28" s="22" t="str">
+        <f aca="false">IF(DATEVALUE(A28)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
+        <v>offen</v>
+      </c>
+      <c r="F28" s="30" t="n">
+        <f aca="false">DATEVALUE(A28)-DATEVALUE($B$3)</f>
+        <v>184</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>599</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>600</v>
+      </c>
+      <c r="E29" s="16" t="str">
+        <f aca="false">IF(DATEVALUE(A29)&lt;DATEVALUE($B$3),"abgelaufen","offen")</f>
+        <v>offen</v>
+      </c>
+      <c r="F29" s="31" t="n">
+        <f aca="false">DATEVALUE(A29)-DATEVALUE($B$3)</f>
         <v>311</v>
       </c>
-      <c r="G25" s="18" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="32" t="s">
-        <v>497</v>
-      </c>
-      <c r="D27" s="32" t="n">
-        <f aca="false">COUNTIF(E6:E25,"offen")</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="32" t="s">
-        <v>498</v>
-      </c>
-      <c r="D28" s="32" t="n">
-        <f aca="false">IFERROR(SMALL(F6:F25,COUNTIF(F6:F25,"&lt;0")+1),"-")</f>
+      <c r="G29" s="18" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="32" t="s">
+        <v>601</v>
+      </c>
+      <c r="D31" s="32" t="n">
+        <f aca="false">COUNTIF(E6:E29,"offen")</f>
         <v>16</v>
       </c>
     </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="32" t="s">
+        <v>602</v>
+      </c>
+      <c r="D32" s="32" t="n">
+        <f aca="false">IFERROR(SMALL(F6:F29,COUNTIF(F6:F29,"&lt;0")+1),"-")</f>
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:G25"/>
+  <autoFilter ref="A5:G29"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -5216,7 +6037,7 @@
     <tabColor rgb="FFBF8F00"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5229,7 +6050,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>499</v>
+        <v>603</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -5240,13 +6061,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
-        <v>500</v>
+        <v>604</v>
       </c>
       <c r="C3" s="33" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>501</v>
+        <v>605</v>
       </c>
       <c r="E3" s="34"/>
       <c r="F3" s="34"/>
@@ -5254,7 +6075,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="12" t="s">
-        <v>502</v>
+        <v>606</v>
       </c>
       <c r="C4" s="33" t="n">
         <v>1</v>
@@ -5262,30 +6083,30 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>503</v>
+        <v>607</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>504</v>
+        <v>608</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>505</v>
+        <v>609</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>506</v>
+        <v>610</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>507</v>
+        <v>611</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>508</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="n">
-        <f aca="false">RANK(F7,$F$7:$F$18)</f>
+        <f aca="false">RANK(F7,$F$7:$F$20)</f>
         <v>3</v>
       </c>
       <c r="B7" s="17" t="str">
@@ -5293,7 +6114,7 @@
         <v>Eurostars 3 (Call 11 / Call 12)</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>509</v>
+        <v>613</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">01_EU_Programme!N3</f>
@@ -5308,12 +6129,12 @@
         <v>7</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>510</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="37" t="n">
-        <f aca="false">RANK(F8,$F$7:$F$18)</f>
+        <f aca="false">RANK(F8,$F$7:$F$20)</f>
         <v>1</v>
       </c>
       <c r="B8" s="23" t="str">
@@ -5321,7 +6142,7 @@
         <v>EuroHPC AI Factories - Zugang zu Rechenkapazitaet</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>509</v>
+        <v>613</v>
       </c>
       <c r="D8" s="22" t="n">
         <f aca="false">01_EU_Programme!N14</f>
@@ -5336,12 +6157,12 @@
         <v>9</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>511</v>
+        <v>615</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="35" t="n">
-        <f aca="false">RANK(F9,$F$7:$F$18)</f>
+        <f aca="false">RANK(F9,$F$7:$F$20)</f>
         <v>2</v>
       </c>
       <c r="B9" s="17" t="str">
@@ -5349,7 +6170,7 @@
         <v>Forschungszulage (FZulG)</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>512</v>
+        <v>616</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">02_DE_Programme!N3</f>
@@ -5364,20 +6185,20 @@
         <v>8</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>513</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="n">
-        <f aca="false">RANK(F10,$F$7:$F$18)</f>
-        <v>4</v>
+        <f aca="false">RANK(F10,$F$7:$F$20)</f>
+        <v>5</v>
       </c>
       <c r="B10" s="23" t="str">
         <f aca="false">01_EU_Programme!B7</f>
         <v>EIC Accelerator Open</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>509</v>
+        <v>613</v>
       </c>
       <c r="D10" s="22" t="n">
         <f aca="false">01_EU_Programme!N7</f>
@@ -5392,20 +6213,20 @@
         <v>5</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>514</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="35" t="n">
-        <f aca="false">RANK(F11,$F$7:$F$18)</f>
-        <v>7</v>
+        <f aca="false">RANK(F11,$F$7:$F$20)</f>
+        <v>9</v>
       </c>
       <c r="B11" s="17" t="str">
         <f aca="false">01_EU_Programme!B5</f>
         <v>EIC Pathfinder Challenges 2026</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>509</v>
+        <v>613</v>
       </c>
       <c r="D11" s="16" t="n">
         <f aca="false">01_EU_Programme!N5</f>
@@ -5420,20 +6241,20 @@
         <v>4</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>515</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="n">
-        <f aca="false">RANK(F12,$F$7:$F$18)</f>
-        <v>4</v>
+        <f aca="false">RANK(F12,$F$7:$F$20)</f>
+        <v>5</v>
       </c>
       <c r="B12" s="23" t="str">
         <f aca="false">02_DE_Programme!B5</f>
         <v>KMU-innovativ: IKT (inkl. Kuenstliche Intelligenz)</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>512</v>
+        <v>616</v>
       </c>
       <c r="D12" s="22" t="n">
         <f aca="false">02_DE_Programme!N5</f>
@@ -5448,20 +6269,20 @@
         <v>5</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>516</v>
+        <v>620</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="35" t="n">
-        <f aca="false">RANK(F13,$F$7:$F$18)</f>
-        <v>7</v>
+        <f aca="false">RANK(F13,$F$7:$F$20)</f>
+        <v>9</v>
       </c>
       <c r="B13" s="17" t="str">
         <f aca="false">02_DE_Programme!B4</f>
         <v>ZIM - Zentrales Innovationsprogramm Mittelstand</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>512</v>
+        <v>616</v>
       </c>
       <c r="D13" s="16" t="n">
         <f aca="false">02_DE_Programme!N4</f>
@@ -5476,20 +6297,20 @@
         <v>4</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>517</v>
+        <v>621</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="37" t="n">
-        <f aca="false">RANK(F14,$F$7:$F$18)</f>
-        <v>12</v>
+        <f aca="false">RANK(F14,$F$7:$F$20)</f>
+        <v>14</v>
       </c>
       <c r="B14" s="23" t="str">
         <f aca="false">01_EU_Programme!B12</f>
         <v>Horizon Europe Cluster 4 - Digital, Industry &amp; Space</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>509</v>
+        <v>613</v>
       </c>
       <c r="D14" s="22" t="n">
         <f aca="false">01_EU_Programme!N12</f>
@@ -5504,20 +6325,20 @@
         <v>1</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>518</v>
+        <v>622</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="35" t="n">
-        <f aca="false">RANK(F15,$F$7:$F$18)</f>
-        <v>10</v>
+        <f aca="false">RANK(F15,$F$7:$F$20)</f>
+        <v>12</v>
       </c>
       <c r="B15" s="17" t="str">
         <f aca="false">01_EU_Programme!B6</f>
         <v>EIC Transition</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>509</v>
+        <v>613</v>
       </c>
       <c r="D15" s="16" t="n">
         <f aca="false">01_EU_Programme!N6</f>
@@ -5532,20 +6353,20 @@
         <v>3</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>519</v>
+        <v>623</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="n">
-        <f aca="false">RANK(F16,$F$7:$F$18)</f>
-        <v>4</v>
+        <f aca="false">RANK(F16,$F$7:$F$20)</f>
+        <v>5</v>
       </c>
       <c r="B16" s="23" t="str">
         <f aca="false">01_EU_Programme!B23</f>
         <v>EIC Seal of Excellence / Sovereignty (STEP) Seal</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>509</v>
+        <v>613</v>
       </c>
       <c r="D16" s="22" t="n">
         <f aca="false">01_EU_Programme!N23</f>
@@ -5560,20 +6381,20 @@
         <v>5</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>520</v>
+        <v>624</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="35" t="n">
-        <f aca="false">RANK(F17,$F$7:$F$18)</f>
-        <v>7</v>
+        <f aca="false">RANK(F17,$F$7:$F$20)</f>
+        <v>9</v>
       </c>
       <c r="B17" s="17" t="str">
         <f aca="false">02_DE_Programme!B11</f>
         <v>Landesprogramme (bundeslandspezifisch)</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>512</v>
+        <v>616</v>
       </c>
       <c r="D17" s="16" t="n">
         <f aca="false">02_DE_Programme!N11</f>
@@ -5588,43 +6409,99 @@
         <v>4</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>521</v>
+        <v>625</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="37" t="n">
-        <f aca="false">RANK(F18,$F$7:$F$18)</f>
-        <v>10</v>
+        <f aca="false">RANK(F18,$F$7:$F$20)</f>
+        <v>4</v>
       </c>
       <c r="B18" s="23" t="str">
+        <f aca="false">02_DE_Programme!B12</f>
+        <v>SPRIND - Bundesagentur fuer Sprunginnovationen</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>616</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <f aca="false">02_DE_Programme!N12</f>
+        <v>4</v>
+      </c>
+      <c r="E18" s="22" t="n">
+        <f aca="false">02_DE_Programme!O12</f>
+        <v>2</v>
+      </c>
+      <c r="F18" s="38" t="n">
+        <f aca="false">D18*$C$3-E18*$C$4</f>
+        <v>6</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="35" t="n">
+        <f aca="false">RANK(F19,$F$7:$F$20)</f>
+        <v>5</v>
+      </c>
+      <c r="B19" s="17" t="str">
+        <f aca="false">01_EU_Programme!B26</f>
+        <v>Eureka Innowwide</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">01_EU_Programme!N26</f>
+        <v>3</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <f aca="false">01_EU_Programme!O26</f>
+        <v>1</v>
+      </c>
+      <c r="F19" s="36" t="n">
+        <f aca="false">D19*$C$3-E19*$C$4</f>
+        <v>5</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="37" t="n">
+        <f aca="false">RANK(F20,$F$7:$F$20)</f>
+        <v>12</v>
+      </c>
+      <c r="B20" s="23" t="str">
         <f aca="false">01_EU_Programme!B17</f>
         <v>Eureka Globalstars / Network Projects</v>
       </c>
-      <c r="C18" s="24" t="s">
-        <v>509</v>
-      </c>
-      <c r="D18" s="22" t="n">
+      <c r="C20" s="24" t="s">
+        <v>613</v>
+      </c>
+      <c r="D20" s="22" t="n">
         <f aca="false">01_EU_Programme!N17</f>
         <v>3</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E20" s="22" t="n">
         <f aca="false">01_EU_Programme!O17</f>
         <v>3</v>
       </c>
-      <c r="F18" s="38" t="n">
-        <f aca="false">D18*$C$3-E18*$C$4</f>
+      <c r="F20" s="38" t="n">
+        <f aca="false">D20*$C$3-E20*$C$4</f>
         <v>3</v>
       </c>
-      <c r="G18" s="24" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="39" t="s">
-        <v>523</v>
-      </c>
-      <c r="G20" s="40" t="s">
-        <v>524</v>
+      <c r="G20" s="24" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="39" t="s">
+        <v>629</v>
+      </c>
+      <c r="G22" s="40" t="s">
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -5648,7 +6525,7 @@
     <tabColor rgb="FF7F7F7F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5660,7 +6537,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>525</v>
+        <v>631</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -5669,19 +6546,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>527</v>
+        <v>633</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>528</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5689,16 +6566,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>529</v>
+        <v>635</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>530</v>
+        <v>636</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>531</v>
+        <v>637</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>532</v>
+        <v>638</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5706,16 +6583,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>533</v>
+        <v>639</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>530</v>
+        <v>636</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>534</v>
+        <v>640</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>535</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5723,16 +6600,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>536</v>
+        <v>642</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>537</v>
+        <v>643</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>538</v>
+        <v>644</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>539</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5740,16 +6617,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>540</v>
+        <v>646</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>541</v>
+        <v>647</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>542</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5757,16 +6634,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>543</v>
+        <v>649</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>544</v>
+        <v>650</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>545</v>
+        <v>651</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5774,16 +6651,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>546</v>
+        <v>652</v>
       </c>
       <c r="C9" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>547</v>
+        <v>653</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>548</v>
+        <v>654</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5791,16 +6668,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>549</v>
+        <v>655</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>550</v>
+        <v>656</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>551</v>
+        <v>657</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5808,16 +6685,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>552</v>
+        <v>658</v>
       </c>
       <c r="C11" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>553</v>
+        <v>659</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>554</v>
+        <v>660</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5825,16 +6702,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>555</v>
+        <v>661</v>
       </c>
       <c r="C12" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>556</v>
+        <v>662</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>557</v>
+        <v>663</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5842,16 +6719,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>558</v>
+        <v>664</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>559</v>
+        <v>665</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>560</v>
+        <v>666</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5859,16 +6736,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>561</v>
+        <v>667</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>562</v>
+        <v>668</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>563</v>
+        <v>669</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5876,16 +6753,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>564</v>
+        <v>670</v>
       </c>
       <c r="C15" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>565</v>
+        <v>671</v>
       </c>
       <c r="E15" s="42" t="s">
-        <v>566</v>
+        <v>672</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5893,16 +6770,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>567</v>
+        <v>673</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>568</v>
+        <v>674</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>569</v>
+        <v>675</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>570</v>
+        <v>676</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5910,16 +6787,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>571</v>
+        <v>677</v>
       </c>
       <c r="C17" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>572</v>
+        <v>678</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>573</v>
+        <v>679</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5927,16 +6804,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>574</v>
+        <v>680</v>
       </c>
       <c r="C18" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>575</v>
+        <v>681</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>576</v>
+        <v>682</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5944,16 +6821,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>577</v>
+        <v>683</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>578</v>
+        <v>684</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>579</v>
+        <v>685</v>
       </c>
       <c r="E19" s="42" t="s">
-        <v>580</v>
+        <v>686</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5961,16 +6838,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>581</v>
+        <v>687</v>
       </c>
       <c r="C20" s="27" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>582</v>
+        <v>688</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>583</v>
+        <v>689</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5978,16 +6855,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>584</v>
+        <v>690</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>585</v>
+        <v>691</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>586</v>
+        <v>692</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>587</v>
+        <v>693</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5995,16 +6872,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>588</v>
+        <v>694</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>589</v>
+        <v>695</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>590</v>
+        <v>696</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>591</v>
+        <v>697</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6012,16 +6889,101 @@
         <v>20</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>592</v>
-      </c>
-      <c r="C23" s="27" t="s">
+        <v>698</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>699</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>701</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>684</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>702</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>705</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>707</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>708</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>709</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>711</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>712</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>715</v>
+      </c>
+      <c r="C28" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="18" t="s">
-        <v>593</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>594</v>
+      <c r="D28" s="24" t="s">
+        <v>716</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -6048,6 +7010,11 @@
     <hyperlink ref="E20" r:id="rId17" display="https://www.ideal-ist.eu/news/horizon-europe-cluster-4-work-programme-2026-2027-adopted"/>
     <hyperlink ref="E21" r:id="rId18" display="https://www.vdivde-it.de/de/kmu-innovativ-ikt"/>
     <hyperlink ref="E22" r:id="rId19" display="https://exist.de/wp-content/uploads/2024/10/260609_Handbuch_EFT_2026_barrierefrei.pdf"/>
+    <hyperlink ref="E23" r:id="rId20" display="https://www.bundesanzeiger.de/pub/publication/H4hLAtOVVOn1N7yG6vR"/>
+    <hyperlink ref="E24" r:id="rId21" display="https://www.gesetze-im-internet.de/fzulg/__3.html"/>
+    <hyperlink ref="E25" r:id="rId22" display="https://www.bafa.de/DE/Wirtschaft/Beratung_Finanzierung/Invest/invest_node.html"/>
+    <hyperlink ref="E26" r:id="rId23" display="https://www.sprind.org/en/actions/challenges/next-frontier-ai"/>
+    <hyperlink ref="E27" r:id="rId24" display="https://www.eurekanetwork.org/programmes-and-calls/eureka-clusters/xecs-call-6-2026/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
